--- a/files/수정본/코드베인_데이터_테이블.xlsx
+++ b/files/수정본/코드베인_데이터_테이블.xlsx
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>EFF_SELF_HP_COST</t>
+          <t>EFF_SELF_HP_COST · 소모 후 잔여 HP는 최소 1로 클램프한다</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>EFF_REVIVE_PLAYER</t>
+          <t>EFF_REVIVE_PLAYER · 쿨타임 120초 (유대 4등급 시 96초)</t>
         </is>
       </c>
     </row>
@@ -1313,17 +1313,83 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>동행자 현재 HP &lt; 최대 HP × 30%</t>
+          <t>동행자 현재 HP &lt; 최대 HP × 40%</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1,350 미만이면 차단</t>
+          <t>1,800 미만이면 차단</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>본편 47p·77p·89p와 BT 10p를 30%로 통일</t>
+          <t>본편 47p·77p·89p와 BT 14p를 40%로 통일. 30%로 두면 비용(최대HP×30%)과 같아져 부활 직후 잔여 HP가 0이 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>스태미나</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>기본 계수 × 플레이어 레벨 × 0.5 (역할군 무관 공통)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>100 × 10 × 0.5 = 500</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>가드·회피 전용 자원. 명혈과 별개로 관리한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>다회차 난이도 계수</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>공격력·방어력·체력에 회차 계수를 곱한다 (1회차 1.00 / 2회차 1.15 / 3회차 이상 1.30)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>4,500 × 1.15 = 5,175</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>개선안·커스터마이징 102p 반영. 명혈·스태미나에는 적용하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>단수 처리</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>모든 산출 결과는 소수점 올림</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>250.4 → 251</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>본편 87p 표기와 일치</t>
         </is>
       </c>
     </row>
@@ -1528,17 +1594,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="4" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="9"/>
+    <col width="17" customWidth="1" min="10" max="11"/>
+    <col width="15" customWidth="1" min="12" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -1551,7 +1618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>모듈러 서브트리가 [AI 파라미터 키]로 이 행을 참조해 값을 주입받는다. 거리 단위는 언리얼 유닛(uu, 1uu = 1cm).</t>
+          <t>모듈러 서브트리가 [AI 파라미터 키]로 이 행을 참조해 값을 주입받는다. 거리 단위는 언리얼 유닛(uu, 1uu = 1cm). 명혈(Ichor)과 스태미나(Stamina)는 별개 자원이다 — 명혈은 연혈 시전, 스태미나는 가드·회피에 쓴다. 임계값은 [동행자 테이블·명혈 최대치] 대비 비율(%)이므로 캐릭터마다 절대값이 다르다. SkillRange는 본편 77p 역할군 선호 거리(인파이팅 0~2m / 밸런서 2~5m / 백라인 3~7m) 밴드를 따르며, 추종 이탈 한계 700uu를 넘지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1573,35 +1640,55 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>StaminaThreshold</t>
+          <t>IchorThresholdPct(%)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>StaminaThresholdPct(%)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>ApproachSpeed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>StrafeSpeed</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>SkillRange_Min</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>SkillRange_Max</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>SkillChance(%)</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>AtkSkillChance(%)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>BuffSkillChance(%)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>GuardChance(%)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>TauntChance(%)</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>설계 의도</t>
         </is>
@@ -1624,26 +1711,38 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>500</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>200</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>200</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>가드·대검 스킬 즉시 사용을 위해 항상 비축</t>
+      <c r="K5" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>스태미나를 60% 이상 비축해 연속 가드를 유지한다. 인파이팅 0~2m로 적 정면을 점유하고, 유저 위기 시 도발로 시선을 탈취한다.</t>
         </is>
       </c>
     </row>
@@ -1664,26 +1763,38 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>550</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>부활 연혈 시전을 위한 여유 자원 상시 확보</t>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>명혈 여유분이 가장 커 치유의 파문(코스트 30)을 상시 돌린다. 백라인 3~6m에서 도끼창 리치로 지원한다.</t>
         </is>
       </c>
     </row>
@@ -1704,26 +1815,38 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>100</v>
-      </c>
       <c r="H7" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I7" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>임계값이 낮아 공격을 끝까지 퍼붓는다</t>
+      <c r="K7" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>임계값이 낮아 공격을 끝까지 퍼붓는다. 밸런서 2~5m에서 유저와 공수 리듬을 교차시킨다.</t>
         </is>
       </c>
     </row>
@@ -1744,26 +1867,38 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>850</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>가장 호전적. 최고속으로 배후 점유</t>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>가장 호전적. 최고속으로 접근해 배후 판정(TARGET_BACK)을 점유한다. 버프 선행 후 화력을 몰아친다.</t>
         </is>
       </c>
     </row>
@@ -1784,26 +1919,38 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>600</v>
-      </c>
       <c r="H9" s="4" t="n">
-        <v>1800</v>
+        <v>350</v>
       </c>
       <c r="I9" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>평타보다 연혈 비중이 압도적</t>
+      <c r="K9" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>평타보다 연혈 비중이 압도적. 백라인 3.5~7m를 유지하며 최소 사거리 안쪽으로 붙으면 이탈한다.</t>
         </is>
       </c>
     </row>
@@ -1824,26 +1971,38 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>800</v>
-      </c>
       <c r="H10" s="4" t="n">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="I10" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="J10" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>최장 사거리. 접근당하면 공격 브랜치 이탈</t>
+      <c r="K10" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>최장 사거리. 최소 사거리(400uu) 안쪽으로 접근당하면 공격 브랜치를 이탈해 후퇴한다.</t>
         </is>
       </c>
     </row>
@@ -1859,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3068,6 +3227,118 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SKL_COMMON_TAUNT</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>COMMON</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>NAME_SKL_COMMON_TAUNT</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>DESC_SKL_COMMON_TAUNT</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>ICON_SKL_COMMON_TAUNT</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>시선 탈취</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>EFF_TAUNT</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SKL_COMMON_GUARD</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>COMMON</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>DEFENSE</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>NAME_SKL_COMMON_GUARD</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>DESC_SKL_COMMON_GUARD</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>ICON_SKL_COMMON_GUARD</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>가드</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>EFF_GUARD_STANCE</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -3080,7 +3351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3292,10 +3563,8 @@
           <t>SELF_HP_LOW</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>한 목숨당 3회 제한</t>
-        </is>
+      <c r="J7" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -4423,6 +4692,190 @@
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>개선안 : 상시 오라</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>EFF_ICHOR_GAIN</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ICHOR_GAIN</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>ICHOR</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>ATK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>평타 1회 적중당 명혈 4 회복. 본편 48p·77p '직접 공격과 흡혈로 자원을 수급한다'의 데이터 구현체 — 명혈은 패시브 재생하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>EFF_ICHOR_DRAIN</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ICHOR_GAIN</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>ICHOR</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>TARGET_DEAD</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>흡혈(적 처치) 시 명혈 12 회복. 근접 역할군이 원거리보다 자원 회전이 빠른 이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>EFF_TAUNT</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ENEMY_AREA</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>AREA</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>AGGRO_FORCE</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>PLAYER_HEALING</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>본편 76p 2순위 · 77p '유저가 재생력을 마시면 공격적 스탠스로 전환' · 89p '탱커형은 어그로 전용 스킬 보유'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>EFF_GUARD_STANCE</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>GUARD</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>STAMINA</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>ENEMY_ATTACKING</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>가드 1회당 스태미나 12 소모. 본편 3p 설계 목표 '가드 빈도를 달리해'의 데이터 구현체</t>
         </is>
       </c>
     </row>
@@ -4438,11 +4891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="10"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -4455,57 +4909,62 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>점수 체계는 1·2·3·5점 + '-'(교환 불가). 4점을 두지 않아 5점의 희소 가치를 강조한다.</t>
+          <t>점수 체계는 1·2·3·5점 + 'T' + '-'. 4점을 두지 않아 5점의 희소 가치를 강조한다. 'T' = 특수 대화 트리거(선물 교환 대상이 아니라 전용 대사가 출력되는 아이템), '-' = 교환 불가. 본편 캐릭터 카드의 '특수 대화' 항목은 이 시트의 T 셀과 1:1로 대응한다. 5점은 캐릭터당 3~5종으로 유지한다. 본편 카드는 표기명이 아닌 ITEM_ID 로 이 시트를 참조한다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>ITEM_ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>기호품</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>이오</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>루이</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>야쿠모</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>데이비드</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>무라사메</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>코코</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>미아</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>잭</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>에바</t>
         </is>
@@ -4514,20 +4973,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>35mm필름</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>3</v>
+          <t>GIFT_FILM_35MM</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>35mm 필름</t>
+        </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -4539,91 +5000,106 @@
         <v>2</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>GIFT_ANTIQUE_COIN</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
           <t>앤티크 동전</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C6" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>GIFT_COMIC_FADED</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>빛바랜 만화책</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>GIFT_SOAP_ORGANIC</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
           <t>유기농 비누</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>2</v>
@@ -4632,7 +5108,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>3</v>
@@ -4641,23 +5117,28 @@
         <v>3</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>GIFT_PERFUME</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
           <t>향수</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>2</v>
@@ -4666,7 +5147,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>3</v>
@@ -4674,68 +5155,78 @@
       <c r="H9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="n">
+      <c r="I9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>GIFT_CHOCO_FLAKE</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>초콜릿 플레이크</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="G10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>2</v>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
       </c>
       <c r="J10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>GIFT_TEA_FRAGRANT</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>향기로운 홍차</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>2</v>
@@ -4744,72 +5235,82 @@
         <v>2</v>
       </c>
       <c r="H11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="J11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>GIFT_CHEESE</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>치즈</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>GIFT_CAMERA</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>카메라</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
@@ -4817,33 +5318,38 @@
         <v>1</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>GIFT_GEISHA_NOODLE</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
           <t>게이샤 누들</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="G14" s="5" t="n">
         <v>3</v>
       </c>
@@ -4854,18 +5360,23 @@
         <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>GIFT_ICHOR_CANDY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>혈루 사탕</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C15" s="5" t="n">
         <v>3</v>
       </c>
@@ -4888,57 +5399,67 @@
         <v>3</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>GIFT_LIQUOR_LOCAL</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
           <t>민속주</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>GIFT_FLAG_REGION</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
           <t>지방의 깃발</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D17" s="5" t="n">
         <v>1</v>
       </c>
@@ -4958,93 +5479,108 @@
         <v>1</v>
       </c>
       <c r="J17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>GIFT_SPICE</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
           <t>향신료</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>2</v>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
       </c>
       <c r="E18" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>GIFT_GUN_PARTS</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>총 파츠</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>GIFT_COFFEE_BEAN</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>원두 커피</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C20" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>2</v>
@@ -5053,85 +5589,98 @@
         <v>2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>GIFT_INSTRUMENT</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>신품 악기</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="J21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>GIFT_SUSHI_TACOS</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>스시 타코스</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5140,85 +5689,97 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>GIFT_CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>초콜릿</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C23" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="G23" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>GIFT_ODEN_BREAD</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>오뎅 빵</t>
         </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>GIFT_DOLL_MYSTERY</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>수수께끼 인형</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="C25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
@@ -5238,52 +5799,62 @@
         <v>1</v>
       </c>
       <c r="J25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>GIFT_LP_RECORD</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>LP 레코드</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C26" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="G26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>GIFT_TOOLS</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
           <t>공구</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C27" s="5" t="n">
         <v>1</v>
       </c>
@@ -5291,74 +5862,84 @@
         <v>1</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>GIFT_BRANDY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
           <t>브랜디</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="K28" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>GIFT_DOLL_BAGARARI</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
           <t>바가라리 인형</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C29" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>5</v>
@@ -5367,35 +5948,40 @@
         <v>5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="K29" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>GIFT_SEED_FLOWER</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>꽃씨</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>2</v>
@@ -5407,61 +5993,71 @@
         <v>2</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>GIFT_JAM</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>잼</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C31" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="G31" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>GIFT_DOLL_FLUFFY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
           <t>푹신한 인형</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>1</v>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
       </c>
       <c r="D32" s="5" t="n">
         <v>1</v>
@@ -5470,111 +6066,126 @@
         <v>1</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>GIFT_BOOK_LIT</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
           <t>낡은 문학서</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E33" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>GIFT_CIGAR</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
           <t>시가</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C34" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>GIFT_PROTEIN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
           <t>프로틴 파우더</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C35" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>1</v>
@@ -5583,94 +6194,109 @@
         <v>1</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>GIFT_HERB</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
           <t>허브</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>GIFT_BOARDGAME</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
           <t>보드 게임</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C37" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="H37" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>GIFT_FOUNTAIN_PEN</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
           <t>만년필</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>1</v>
@@ -5679,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>2</v>
@@ -5688,29 +6314,34 @@
         <v>2</v>
       </c>
       <c r="J38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>GIFT_SEED_VEGGIE</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
           <t>야채 씨앗</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>2</v>
@@ -5719,79 +6350,92 @@
         <v>2</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>GIFT_ART_SUPPLY</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
           <t>그림도구</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>GIFT_RETRO_GAME</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>레트로 게임</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="C41" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="H41" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5807,7 +6451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5887,7 +6531,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>45</v>
@@ -5918,7 +6562,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>45</v>
@@ -5980,7 +6624,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>60</v>
@@ -6042,7 +6686,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>30</v>
@@ -6173,7 +6817,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>하핫, 실력을 보여줬구나</t>
+          <t>체력이 얼마 없어, 무리하지 마!</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6872,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>30</v>
@@ -6259,7 +6903,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>45</v>
@@ -6290,7 +6934,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>60</v>
@@ -6321,7 +6965,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>45</v>
@@ -6352,7 +6996,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>45</v>
@@ -6383,7 +7027,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>45</v>
@@ -6414,7 +7058,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>60</v>
@@ -6445,7 +7089,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>60</v>
@@ -6476,7 +7120,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>60</v>
@@ -6507,7 +7151,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>60</v>
@@ -6538,7 +7182,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>30</v>
@@ -6569,7 +7213,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>30</v>
@@ -6600,7 +7244,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>45</v>
@@ -6631,7 +7275,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>45</v>
@@ -6755,7 +7399,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>45</v>
@@ -6786,7 +7430,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>30</v>
@@ -6817,7 +7461,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>60</v>
@@ -6848,7 +7492,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>60</v>
@@ -6879,7 +7523,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>60</v>
@@ -6910,7 +7554,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>30</v>
@@ -6941,7 +7585,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>60</v>
@@ -6972,7 +7616,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>60</v>
@@ -7003,7 +7647,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>60</v>
@@ -7034,7 +7678,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>60</v>
@@ -7065,7 +7709,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>60</v>
@@ -7096,7 +7740,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>90</v>
@@ -7175,7 +7819,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Exploration</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -7189,7 +7833,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>30</v>
@@ -7216,7 +7860,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Enemy_Health_Status</t>
+          <t>Player_Potion_Low</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -7251,7 +7895,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>60</v>
@@ -7344,7 +7988,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>60</v>
@@ -7375,7 +8019,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>60</v>
@@ -7406,7 +8050,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>30</v>
@@ -7468,7 +8112,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>60</v>
@@ -7499,7 +8143,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>45</v>
@@ -7530,7 +8174,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>45</v>
@@ -7561,14 +8205,14 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>45</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>저 흰 거… 고치인가?</t>
+          <t>저건 처음 보는 물건인데?</t>
         </is>
       </c>
     </row>
@@ -7592,7 +8236,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>45</v>
@@ -7623,7 +8267,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>45</v>
@@ -7685,14 +8329,45 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>45</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>방심한다면 아픈 꼴을 당하겠는걸</t>
+          <t>슬슬 시작이군, 정신 차려라</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>13004</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>EnemyHealthBrief</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Enemy_Health_Status</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>저 녀석, 이제 얼마 안 남았다!</t>
         </is>
       </c>
     </row>
